--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104531_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104531_W9.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4378</v>
+        <v>3.1445</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7906</v>
+        <v>4.2716</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3528</v>
+        <v>-1.1271</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5842</v>
+        <v>1.5769</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3216</v>
+        <v>-0.3298</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9059</v>
+        <v>1.9067</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8557</v>
+        <v>4.8158</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5372</v>
+        <v>1.5094</v>
       </c>
       <c r="L2" t="n">
-        <v>3.3185</v>
+        <v>3.3064</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.2715</v>
+        <v>-3.2389</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.8588</v>
+        <v>-1.8392</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4263</v>
+        <v>-0.6992</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3035</v>
+        <v>-0.7623</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1228</v>
+        <v>0.0631</v>
       </c>
       <c r="V2" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.228</v>
+        <v>-0.1923</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1049</v>
+        <v>0.0269</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.333</v>
+        <v>-0.2192</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5823</v>
+        <v>-2.4584</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5179</v>
+        <v>-3.8797</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9356</v>
+        <v>1.4214</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7148</v>
+        <v>-0.897</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8871</v>
+        <v>-2.7589</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6019</v>
+        <v>1.8618</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2971</v>
+        <v>-1.5613</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6308</v>
+        <v>-1.1209</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6663</v>
+        <v>-0.4405</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4055</v>
+        <v>0.0871</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3902</v>
+        <v>-0.4324</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0153</v>
+        <v>0.5195</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.4945</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1853</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="4">
@@ -721,55 +721,55 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5262</v>
+        <v>-0.5219</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0872</v>
+        <v>-0.0877</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.439</v>
+        <v>-0.4342</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8407</v>
+        <v>-0.8378</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4676</v>
+        <v>-0.4654</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J4" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="K4" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8927</v>
+        <v>-0.8895</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6286</v>
+        <v>-0.5688</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1633</v>
+        <v>-0.1709</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4653</v>
+        <v>-0.3979</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1717</v>
+        <v>-0.1696</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1717</v>
+        <v>-0.1696</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2547</v>
+        <v>-0.1928</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6937</v>
+        <v>-0.6004</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4723</v>
+        <v>0.1377</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2213</v>
+        <v>-0.7381</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.4559</v>
+        <v>0.1615</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.8713</v>
+        <v>0.1808</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4154</v>
+        <v>-0.0193</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8711</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.7369</v>
+        <v>0.0517</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8658</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5848</v>
+        <v>0.0725</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1344</v>
+        <v>0.129</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4504</v>
+        <v>-0.0565</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4231</v>
+        <v>0.0999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9739</v>
+        <v>0.0487</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5507</v>
+        <v>0.0512</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1853</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5068</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8531</v>
+        <v>-1.3884</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0197</v>
+        <v>0.4431</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8728</v>
+        <v>-1.8315</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1561</v>
+        <v>-0.5834</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1774</v>
+        <v>-1.522</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0213</v>
+        <v>0.9386</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0893</v>
+        <v>0.6897</v>
       </c>
       <c r="K7" t="n">
-        <v>0.052</v>
+        <v>-0.9038</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>1.5935</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0669</v>
+        <v>-1.2731</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1255</v>
+        <v>-0.6182</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0586</v>
+        <v>-0.6549</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1434</v>
+        <v>0.2358</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0696</v>
+        <v>-0.2466</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0738</v>
+        <v>0.4824</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8168</v>
+        <v>-1.6591</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8153</v>
+        <v>-0.8756</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0014</v>
+        <v>-0.7834</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0161</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0128</v>
+        <v>0.0252</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0289</v>
+        <v>-1.0247</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5578</v>
+        <v>0.5486</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1949</v>
+        <v>1.1893</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5738</v>
+        <v>-1.5481</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1821</v>
+        <v>-1.1642</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.64</v>
+        <v>-0.5018</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2389</v>
+        <v>-0.2861</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4011</v>
+        <v>-0.2157</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4617</v>
+        <v>-2.7624</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9574</v>
+        <v>-0.6402</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.4191</v>
+        <v>-2.1222</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4762</v>
+        <v>-3.0773</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1573</v>
+        <v>-0.9252</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3189</v>
+        <v>-2.1521</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9826</v>
+        <v>0.2473</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9453</v>
+        <v>0.2101</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4588</v>
+        <v>-3.3246</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1026</v>
+        <v>-1.1353</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.3563</v>
+        <v>-2.1893</v>
       </c>
       <c r="P9" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0931</v>
+        <v>-1.2299</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1179</v>
+        <v>-0.8389</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0248</v>
+        <v>-0.391</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8599</v>
+        <v>-2.9147</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7419</v>
+        <v>-1.7947</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.118</v>
+        <v>-1.12</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0939</v>
+        <v>-4.5154</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9323</v>
+        <v>-4.0376</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1617</v>
+        <v>-0.4777</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2553</v>
+        <v>-2.0514</v>
       </c>
       <c r="K10" t="n">
-        <v>0.218</v>
+        <v>-2.7589</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>0.7075</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.3493</v>
+        <v>-2.464</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1503</v>
+        <v>-1.2788</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.199</v>
+        <v>-1.1852</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3123</v>
+        <v>-0.3962</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9557</v>
+        <v>-0.3743</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3566</v>
+        <v>-0.0218</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0927</v>
+        <v>0.6311</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>0.6311</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.016</v>
+        <v>-2.9789</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7117</v>
+        <v>1.4705</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3043</v>
+        <v>-4.4494</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.5163</v>
+        <v>-2.4679</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.0286</v>
+        <v>-0.1579</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4877</v>
+        <v>-2.31</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0279</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.7369</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.709</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4884</v>
+        <v>-3.4392</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2917</v>
+        <v>-1.092</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1967</v>
+        <v>-2.3472</v>
       </c>
       <c r="P11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5036</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3266</v>
+        <v>-0.5903</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1769</v>
+        <v>-0.0392</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6429</v>
+        <v>-1.2472</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6429</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2502</v>
+        <v>-3.2019</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.5001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6832</v>
+        <v>-2.7018</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6021</v>
+        <v>-2.6068</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6552</v>
+        <v>0.6494</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.2573</v>
+        <v>-3.2563</v>
       </c>
       <c r="J12" t="n">
-        <v>1.773</v>
+        <v>1.7347</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3409</v>
+        <v>2.3162</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5679</v>
+        <v>-0.5816</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.3751</v>
+        <v>-4.3415</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6857</v>
+        <v>-1.6668</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.6894</v>
+        <v>-2.6747</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3513</v>
+        <v>-1.3007</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1644</v>
+        <v>-1.048</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1869</v>
+        <v>-0.2527</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1568</v>
+        <v>1.1609</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2512</v>
+        <v>-6.1492</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6916</v>
+        <v>-4.6259</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5597</v>
+        <v>-1.5233</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.5753</v>
+        <v>-3.589</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1973</v>
+        <v>-2.2189</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.378</v>
+        <v>-1.3701</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.3187</v>
+        <v>-1.3539</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3933</v>
+        <v>-1.4284</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2566</v>
+        <v>-2.2351</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6986</v>
+        <v>-0.583</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6775</v>
+        <v>-0.5601</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0212</v>
+        <v>-0.0229</v>
       </c>
       <c r="V13" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6429</v>
+        <v>-0.6311</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-20.1476</v>
+        <v>-19.7935</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.3777</v>
+        <v>-2.345299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-17.7699</v>
+        <v>-17.4481</v>
       </c>
       <c r="G14" t="n">
-        <v>-19.5902</v>
+        <v>-19.5667</v>
       </c>
       <c r="H14" t="n">
-        <v>-12.8202</v>
+        <v>-12.8507</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.7701</v>
+        <v>-6.7159</v>
       </c>
       <c r="J14" t="n">
-        <v>5.080100000000001</v>
+        <v>4.862900000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.3966</v>
+        <v>-1.5704</v>
       </c>
       <c r="L14" t="n">
-        <v>6.476699999999999</v>
+        <v>6.432999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-24.6703</v>
+        <v>-24.4296</v>
       </c>
       <c r="N14" t="n">
-        <v>-11.4234</v>
+        <v>-11.2809</v>
       </c>
       <c r="O14" t="n">
-        <v>-13.2469</v>
+        <v>-13.149</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.4759</v>
+        <v>-12.5199</v>
       </c>
       <c r="R14" t="n">
-        <v>13.6101</v>
+        <v>13.6581</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.579999999999999</v>
+        <v>-5.2497</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.716000000000001</v>
+        <v>-5.3691</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1359999999999999</v>
+        <v>0.1195</v>
       </c>
       <c r="V14" t="n">
-        <v>3.8886</v>
+        <v>3.8846</v>
       </c>
       <c r="W14" t="n">
-        <v>10.7344</v>
+        <v>10.6806</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.8456</v>
+        <v>-6.7959</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.2798</v>
+        <v>7.0641</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9881</v>
+        <v>6.0775</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2916</v>
+        <v>0.9866</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0883</v>
+        <v>3.092</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2957</v>
+        <v>4.2939</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2074</v>
+        <v>-1.2019</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9026</v>
+        <v>3.8781</v>
       </c>
       <c r="K15" t="n">
-        <v>3.716</v>
+        <v>3.6919</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8143</v>
+        <v>-0.7861</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5797</v>
+        <v>0.6019</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2842</v>
+        <v>1.0616</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0998</v>
+        <v>0.0205</v>
       </c>
       <c r="U15" t="n">
-        <v>1.384</v>
+        <v>1.0412</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.6859</v>
+        <v>6.0767</v>
       </c>
       <c r="E16" t="n">
-        <v>5.067</v>
+        <v>4.6672</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6189</v>
+        <v>1.4095</v>
       </c>
       <c r="G16" t="n">
-        <v>6.4266</v>
+        <v>6.4083</v>
       </c>
       <c r="H16" t="n">
-        <v>5.6856</v>
+        <v>5.6649</v>
       </c>
       <c r="I16" t="n">
-        <v>0.741</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>6.0737</v>
+        <v>6.034</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2154</v>
+        <v>5.1776</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8583</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3529</v>
+        <v>0.3743</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4701</v>
+        <v>0.4873</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0817</v>
+        <v>1.4831</v>
       </c>
       <c r="T16" t="n">
-        <v>0.738</v>
+        <v>0.3875</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3437</v>
+        <v>1.0956</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.9566</v>
+        <v>-2.9529</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.6433</v>
+        <v>5.3522</v>
       </c>
       <c r="E17" t="n">
-        <v>4.4612</v>
+        <v>4.2151</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1821</v>
+        <v>1.1371</v>
       </c>
       <c r="G17" t="n">
-        <v>4.015</v>
+        <v>4.2243</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2799</v>
+        <v>0.2399</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7352</v>
+        <v>3.9843</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4035</v>
+        <v>5.184</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2743</v>
+        <v>0.4999</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1292</v>
+        <v>4.6842</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3885</v>
+        <v>-0.9598</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0055</v>
+        <v>-0.2599</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.394</v>
+        <v>-0.6998</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1449</v>
+        <v>0.7896</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6079</v>
+        <v>0.2179</v>
       </c>
       <c r="U17" t="n">
-        <v>0.463</v>
+        <v>0.5718</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5463</v>
+        <v>1.4764</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7997</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2534</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.0843</v>
+        <v>4.8366</v>
       </c>
       <c r="E18" t="n">
-        <v>3.7687</v>
+        <v>4.656</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3156</v>
+        <v>0.1806</v>
       </c>
       <c r="G18" t="n">
-        <v>4.209</v>
+        <v>4.0049</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2161</v>
+        <v>2.2804</v>
       </c>
       <c r="I18" t="n">
-        <v>3.9929</v>
+        <v>1.7245</v>
       </c>
       <c r="J18" t="n">
-        <v>5.2014</v>
+        <v>4.3741</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5022</v>
+        <v>1.2615</v>
       </c>
       <c r="L18" t="n">
-        <v>4.6992</v>
+        <v>3.1126</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.3692</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2861</v>
+        <v>1.0189</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7063</v>
+        <v>-1.3881</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4688</v>
+        <v>0.0593</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2571</v>
+        <v>-0.3719</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2117</v>
+        <v>0.4313</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4783</v>
+        <v>0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.792</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3856</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.1279</v>
+        <v>1.852</v>
       </c>
       <c r="E19" t="n">
-        <v>4.6151</v>
+        <v>3.642</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4872</v>
+        <v>-1.79</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6959</v>
+        <v>2.7043</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="I19" t="n">
-        <v>3.044</v>
+        <v>3.0355</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3321</v>
+        <v>2.3168</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6132</v>
+        <v>-0.6173</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9453</v>
+        <v>2.934</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3638</v>
+        <v>0.3875</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2652</v>
+        <v>0.2861</v>
       </c>
       <c r="O19" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2939</v>
+        <v>2.0127</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6816</v>
+        <v>0.7428</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6123</v>
+        <v>1.2699</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.6351</v>
+        <v>-2.6374</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7355</v>
+        <v>1.7205</v>
       </c>
       <c r="X19" t="n">
-        <v>-4.3707</v>
+        <v>-4.3579</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1754</v>
+        <v>0.5221</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9686</v>
+        <v>0.0113</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2068</v>
+        <v>0.5107</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5131</v>
+        <v>0.518</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8037</v>
+        <v>0.8069</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2905</v>
+        <v>-0.2889</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7685</v>
+        <v>0.7597</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0968</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2554</v>
+        <v>-0.2417</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9591</v>
+        <v>0.2984</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1735</v>
+        <v>0.232</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2144</v>
+        <v>0.0664</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>0.4498</v>
+        <v>0.4584</v>
       </c>
     </row>
     <row r="21">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1858</v>
+        <v>0.1281</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9933</v>
+        <v>0.9893</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8075</v>
+        <v>-0.8612</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0043</v>
+        <v>-0.9962</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.863</v>
+        <v>-0.8562</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1413</v>
+        <v>-0.14</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1093</v>
+        <v>0.1089</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1135</v>
+        <v>-1.1052</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,19 +2092,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0974</v>
+        <v>0.0349</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3061</v>
+        <v>0.244</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8083</v>
+        <v>-0.6756</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8587</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0504</v>
+        <v>0.1868</v>
       </c>
       <c r="G22" t="n">
-        <v>0.204</v>
+        <v>0.2076</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4199</v>
+        <v>0.4221</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0828</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2986</v>
+        <v>0.3014</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2825</v>
+        <v>-0.1579</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0738</v>
+        <v>0.0512</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Z. HICKS</t>
+          <t>D. ENNIS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5121</v>
+        <v>-1.2672</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8703</v>
+        <v>-1.6095</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6418</v>
+        <v>0.3423</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9593</v>
+        <v>-0.5149</v>
       </c>
       <c r="H23" t="n">
-        <v>0.163</v>
+        <v>-1.2662</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1222</v>
+        <v>0.7513</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6798</v>
+        <v>1.378</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0693</v>
+        <v>-0.0732</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.749</v>
+        <v>1.4511</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2795</v>
+        <v>-1.8929</v>
       </c>
       <c r="N23" t="n">
-        <v>0.09370000000000001</v>
+        <v>-1.1931</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3732</v>
+        <v>-0.6998</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>0.313</v>
+        <v>0.0185</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1905</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5036</v>
+        <v>0.7297</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. ENNIS</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8728</v>
+        <v>-1.2967</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0175</v>
+        <v>-3.4643</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1447</v>
+        <v>2.1676</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4868</v>
+        <v>0.8741</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2596</v>
+        <v>1.4274</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7728</v>
+        <v>-0.5533</v>
       </c>
       <c r="J24" t="n">
-        <v>1.4334</v>
+        <v>0.9588</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0457</v>
+        <v>1.0267</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4791</v>
+        <v>-0.0679</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9202</v>
+        <v>-0.0847</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2139</v>
+        <v>0.4007</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7063</v>
+        <v>-0.4854</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4537</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-4.5526</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6109</v>
+        <v>0.6306</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1825</v>
+        <v>-0.0283</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5716</v>
+        <v>0.6589</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3214</v>
+        <v>0.1578</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>Z. HICKS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8417</v>
+        <v>-1.6607</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3456</v>
+        <v>-0.874</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5039</v>
+        <v>-0.7866</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8885</v>
+        <v>-0.9557</v>
       </c>
       <c r="H25" t="n">
-        <v>1.4271</v>
+        <v>0.1691</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5386</v>
+        <v>-1.1248</v>
       </c>
       <c r="J25" t="n">
-        <v>1.0042</v>
+        <v>-0.6835</v>
       </c>
       <c r="K25" t="n">
-        <v>1.0523</v>
+        <v>0.0689</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0481</v>
+        <v>-0.7524</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1157</v>
+        <v>-0.2722</v>
       </c>
       <c r="N25" t="n">
-        <v>0.3748</v>
+        <v>0.1002</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4904</v>
+        <v>-0.3724</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.9488</v>
+        <v>0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.5367</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9421</v>
+        <v>0.1568</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9739</v>
+        <v>-0.1906</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0317</v>
+        <v>0.3474</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>20.1475</v>
+        <v>20.9316</v>
       </c>
       <c r="E26" t="n">
-        <v>17.7699</v>
+        <v>17.4482</v>
       </c>
       <c r="F26" t="n">
-        <v>2.3775</v>
+        <v>3.4834</v>
       </c>
       <c r="G26" t="n">
-        <v>19.59</v>
+        <v>19.5667</v>
       </c>
       <c r="H26" t="n">
-        <v>12.8204</v>
+        <v>12.851</v>
       </c>
       <c r="I26" t="n">
-        <v>6.77</v>
+        <v>6.7157</v>
       </c>
       <c r="J26" t="n">
-        <v>24.6701</v>
+        <v>24.4296</v>
       </c>
       <c r="K26" t="n">
-        <v>11.4232</v>
+        <v>11.2806</v>
       </c>
       <c r="L26" t="n">
-        <v>13.2469</v>
+        <v>13.149</v>
       </c>
       <c r="M26" t="n">
-        <v>-5.08</v>
+        <v>-4.863</v>
       </c>
       <c r="N26" t="n">
-        <v>1.3969</v>
+        <v>1.5702</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.476799999999999</v>
+        <v>-6.433199999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.1341</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q26" t="n">
-        <v>-13.6101</v>
+        <v>-13.658</v>
       </c>
       <c r="R26" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S26" t="n">
-        <v>5.5801</v>
+        <v>6.3876</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1359999999999997</v>
+        <v>-0.1195000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>5.7161</v>
+        <v>6.507400000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.888499999999999</v>
+        <v>-3.884600000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>6.845600000000001</v>
+        <v>6.7959</v>
       </c>
       <c r="X26" t="n">
-        <v>-10.7343</v>
+        <v>-10.6804</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104531_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104531_W9.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.6311</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.7959</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-4.3579</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.4584</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104531_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-10.6804</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
